--- a/results/Int Task Remove ACC -0.6/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.6/Linea_fi_all.xlsx
@@ -1361,7 +1361,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.037245650250663495 +/- 0.004328178272962796</t>
+          <t>0.03727514007667352 +/- 0.004304302516194367</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.011235623709820087 +/- 0.001447406805285511</t>
+          <t>0.011206133883810055 +/- 0.0015036919827758125</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.00448245355352408 +/- 0.004385564481278981</t>
+          <t>-0.0045119433795341 +/- 0.0043801078843288994</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.001834862385321101 +/- 0.0027020330773633383</t>
+          <t>0.0018644569399230537 +/- 0.0027254319313034315</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1801,74 +1801,74 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>-0.000503107428233196 +/- 0.0007009600048728498</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.0018348623853211231 +/- 0.0039279455514737</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>-0.0037585084344480602 +/- 0.005923422370632303</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-0.0037289138798461074 +/- 0.005966367901655453</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-0.00239715892275818 +/- 0.002720285353962235</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.02477064220183489 +/- 0.0036222816035946445</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>-8.878366380585812e-05 +/- 0.0006624157823497777</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.00458715596330278 +/- 0.0014812067187028083</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0.004942290618526202 +/- 0.0018578687322544384</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>-0.0014501331754956826 +/- 0.0015573035947821995</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.20707309854986683 +/- 0.004594405673640789</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.003284995560816806 +/- 0.0024131814302333493</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.13835454276413142 +/- 0.004625184849981595</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>-0.0004735128736312433 +/- 0.0007028317305142174</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.0018348623853211231 +/- 0.0039279455514737</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-0.0037585084344480602 +/- 0.005923422370632303</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-0.0037289138798461074 +/- 0.005966367901655453</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>-0.00239715892275818 +/- 0.002720285353962235</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.02477064220183489 +/- 0.0036222816035946445</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>-8.878366380585812e-05 +/- 0.0006624157823497777</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0.00458715596330278 +/- 0.0014812067187028083</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0.004942290618526202 +/- 0.0018578687322544384</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>-0.0014501331754956826 +/- 0.0016607265873451252</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0.20707309854986683 +/- 0.004594405673640789</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>0.003284995560816806 +/- 0.0024131814302333493</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>0.13835454276413142 +/- 0.004625184849981595</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>-0.000503107428233196 +/- 0.0007009600048728498</t>
-        </is>
-      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>-0.0017460787215152207 +/- 0.002581520631493686</t>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.029357798165137616 +/- 0.0036385659400541563</t>
+          <t>0.02938739271973957 +/- 0.0036028863415054095</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.01415066469719346 +/- 0.003223880791197393</t>
+          <t>0.014150664697193472 +/- 0.0032184620449664664</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0013589364844903916 +/- 0.000701585943104157</t>
+          <t>0.0013884785819793133 +/- 0.0007120809922123419</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.0016248153618906858 +/- 0.002472551788322106</t>
+          <t>0.001683899556868529 +/- 0.002478897098469491</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.001683899556868529 +/- 0.0005766387384325859</t>
+          <t>0.0016543574593796072 +/- 0.0006083090186698344</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.014831261101243377 +/- 0.00313417894929136</t>
+          <t>0.014860864416814723 +/- 0.00315744029034303</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.07819032761310454 +/- 0.00517827929752879</t>
+          <t>0.07815912636505461 +/- 0.00518025292420096</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.09422776911076444 +/- 0.004291731385722156</t>
+          <t>0.09425897035881436 +/- 0.004258598899186173</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.0014736221632772883 +/- 0.0007908286392572012</t>
+          <t>-0.0014441497200117447 +/- 0.0007847643357320394</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.016681402888299467 +/- 0.002982984009167109</t>
+          <t>0.016651930445033925 +/- 0.003017868818015208</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.15287356321839077 +/- 0.004262921742749576</t>
+          <t>-0.15284409077512523 +/- 0.004323919819650645</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.00020630710285879372 +/- 0.002887848295964399</t>
+          <t>-0.00023577954612433727 +/- 0.0028780561428196345</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-0.0318302387267904 +/- 0.005283711259426802</t>
+          <t>-0.031800766283524864 +/- 0.005286094474698948</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-0.024432655467138187 +/- 0.003027065277974537</t>
+          <t>-0.024491600353669284 +/- 0.002995334157730999</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.03560933448573903 +/- 0.0023694480201615774</t>
+          <t>0.03558052434456934 +/- 0.0023696231650795945</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.007404206280610726 +/- 0.001685085429661754</t>
+          <t>-0.007433016421780414 +/- 0.0016789170019399118</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.022615960818208058 +/- 0.0023661178034488427</t>
+          <t>0.022558340535868658 +/- 0.0023336214347450404</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.0002881014116969616 +/- 0.0009019000773551459</t>
+          <t>0.00031691155286664994 +/- 0.0008875207030106256</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.005214635551714275 +/- 0.0007884720359207123</t>
+          <t>0.005243445692883963 +/- 0.000726564114832529</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.09289113622843544 +/- 0.0033442058831916195</t>
+          <t>0.09286139202855441 +/- 0.003359383201307658</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4916,72 +4916,72 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>0.000862581796549644 +/- 0.0016261673923660509</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.11290898274836406 +/- 0.005504204170922269</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.034741225461035065 +/- 0.004114602371395736</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.034741225461035065 +/- 0.004114602371395736</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.03512790005948838 +/- 0.002532452689617296</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.1414039262343843 +/- 0.004017559549054867</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.025669244497322996 +/- 0.002517034265085082</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.02013682331945269 +/- 0.0029775414911601583</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0.012284354550862565 +/- 0.0027553149071078693</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0.050029744199881 +/- 0.0031668843912447766</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0.42560975609756097 +/- 0.005276473509503083</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0.0035990481856037703 +/- 0.00256024831088703</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>0.06177870315288515 +/- 0.005382056601623119</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>0.000832837596668623 +/- 0.0016171656417689705</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.11290898274836406 +/- 0.005504204170922269</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.034741225461035065 +/- 0.004114602371395736</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.034741225461035065 +/- 0.004114602371395736</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.03512790005948838 +/- 0.002532452689617296</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.14137418203450328 +/- 0.004028225703778093</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.025669244497322996 +/- 0.002517034265085082</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.02013682331945269 +/- 0.0029775414911601583</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.012284354550862565 +/- 0.0027553149071078693</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.050029744199881 +/- 0.0031668843912447766</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.42560975609756097 +/- 0.005276473509503083</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.0035990481856037703 +/- 0.00256024831088703</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.06177870315288515 +/- 0.005382056601623119</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.000862581796549644 +/- 0.0016261673923660509</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
